--- a/docs/text/diploma-attachments/cross-encoder-improvements.xlsx
+++ b/docs/text/diploma-attachments/cross-encoder-improvements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AAA\master-thesis\docs\text\diploma-attachments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6724025-1DB4-40A7-B907-A92D234D4458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2DED29-A279-4DF4-A751-B5B2B7829B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{A1D76B35-4FF5-40A4-BD1A-EC3F7AF95CD8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="83">
   <si>
     <t>0.564</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>(Cross-encoder + boost (0.5)) to (cross + no boost)</t>
+  </si>
+  <si>
+    <t>succ_mech</t>
+  </si>
+  <si>
+    <t>succ_users</t>
   </si>
 </sst>
 </file>
@@ -310,7 +316,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -423,16 +429,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -445,10 +490,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -457,9 +500,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -473,7 +513,29 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -788,515 +850,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321504D2-675A-434A-8F61-FABF9CFEC79B}">
-  <dimension ref="C2:AB38"/>
+  <dimension ref="C2:AI41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8.7265625" customWidth="1"/>
     <col min="3" max="3" width="12.6328125" customWidth="1"/>
     <col min="4" max="4" width="9.26953125" customWidth="1"/>
+    <col min="8" max="9" width="12.26953125" customWidth="1"/>
     <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" customWidth="1"/>
+    <col min="34" max="34" width="14.81640625" customWidth="1"/>
+    <col min="35" max="35" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C2" s="6" t="s">
+    <row r="2" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="AC2" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C3" s="13"/>
-      <c r="D3" s="13" t="s">
+    <row r="3" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15" t="s">
+      <c r="H3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="N3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="O3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13" t="s">
+      <c r="S3" s="10"/>
+      <c r="T3" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="U3" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="T3" s="13" t="s">
+      <c r="V3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="W3" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13" t="s">
+      <c r="X3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="AE3" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AF3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AG3" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
+      <c r="AH3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="18" t="s">
+      <c r="H4" s="21">
+        <v>96.41</v>
+      </c>
+      <c r="I4" s="2">
+        <v>49.7</v>
+      </c>
+      <c r="L4" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="2">
+      <c r="M4" s="1">
         <v>0.23</v>
       </c>
-      <c r="L4" s="2">
+      <c r="N4" s="1">
         <v>0.58199999999999996</v>
       </c>
-      <c r="M4" s="3">
+      <c r="O4" s="2">
         <v>87.5</v>
       </c>
-      <c r="Q4" s="22" t="s">
+      <c r="S4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="7">
+      <c r="T4">
         <v>0.60699999999999998</v>
       </c>
-      <c r="S4" s="7">
+      <c r="U4">
         <v>0.86699999999999999</v>
       </c>
-      <c r="T4" s="7">
+      <c r="V4">
         <v>0.28499999999999998</v>
       </c>
-      <c r="U4" s="8">
+      <c r="W4" s="24">
         <v>77.25</v>
       </c>
-      <c r="X4" s="22" t="s">
+      <c r="X4" s="21">
+        <v>96.05</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>53.86</v>
+      </c>
+      <c r="AC4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Y4" s="7">
+      <c r="AD4">
         <v>0.62</v>
       </c>
-      <c r="Z4" s="7">
+      <c r="AE4">
         <v>0.871</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AF4">
         <v>0.307</v>
       </c>
-      <c r="AB4" s="8">
+      <c r="AG4" s="24">
         <v>81.69</v>
       </c>
-    </row>
-    <row r="5" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C5" s="20" t="s">
+      <c r="AH4" s="21">
+        <v>96.88</v>
+      </c>
+      <c r="AI4" s="19">
+        <v>62.79</v>
+      </c>
+    </row>
+    <row r="5" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="19" t="s">
+      <c r="H5" s="21">
+        <v>96.29</v>
+      </c>
+      <c r="I5" s="2">
+        <v>48.95</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="2">
+      <c r="M5" s="1">
         <v>0.23100000000000001</v>
       </c>
-      <c r="L5" s="2">
+      <c r="N5" s="1">
         <v>0.55500000000000005</v>
       </c>
-      <c r="M5" s="3">
+      <c r="O5" s="2">
         <v>87.5</v>
       </c>
-      <c r="Q5" s="20" t="s">
+      <c r="S5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="R5" s="7">
+      <c r="T5">
         <v>0.60499999999999998</v>
       </c>
-      <c r="S5" s="7">
+      <c r="U5">
         <v>0.86599999999999999</v>
       </c>
-      <c r="T5" s="7">
+      <c r="V5">
         <v>0.28000000000000003</v>
       </c>
-      <c r="U5" s="8">
+      <c r="W5" s="25">
         <v>76.72</v>
       </c>
-      <c r="X5" s="20" t="s">
+      <c r="X5" s="21">
+        <v>95.81</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>52.97</v>
+      </c>
+      <c r="AC5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="Y5" s="7">
+      <c r="AD5">
         <v>0.62</v>
       </c>
-      <c r="Z5" s="7">
+      <c r="AE5">
         <v>0.87</v>
       </c>
-      <c r="AA5" s="7">
+      <c r="AF5">
         <v>0.309</v>
       </c>
-      <c r="AB5" s="8">
+      <c r="AG5" s="25">
         <v>81.89</v>
       </c>
-    </row>
-    <row r="6" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C6" s="20" t="s">
+      <c r="AH5" s="21">
+        <v>96.77</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>63.39</v>
+      </c>
+    </row>
+    <row r="6" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="19" t="s">
+      <c r="H6" s="21">
+        <v>95.93</v>
+      </c>
+      <c r="I6" s="2">
+        <v>45.38</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2">
+      <c r="M6" s="1">
         <v>0.19800000000000001</v>
       </c>
-      <c r="L6" s="2">
+      <c r="N6" s="1">
         <v>0.47299999999999998</v>
       </c>
-      <c r="M6" s="3">
+      <c r="O6" s="2">
         <v>79.459999999999994</v>
       </c>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="7">
+      <c r="S6" s="16"/>
+      <c r="T6">
         <v>0</v>
       </c>
-      <c r="S6" s="7">
+      <c r="U6">
         <v>0</v>
       </c>
-      <c r="T6" s="7">
+      <c r="V6">
         <v>0</v>
       </c>
-      <c r="U6" s="8">
+      <c r="W6" s="25">
         <v>0</v>
       </c>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="7">
+      <c r="X6" s="25">
         <v>0</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="Y6" s="6">
         <v>0</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AC6" s="16"/>
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AB6" s="8">
+      <c r="AE6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C7" s="20" t="s">
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="25">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="19" t="s">
+      <c r="H7" s="21">
+        <v>95.69</v>
+      </c>
+      <c r="I7" s="2">
+        <v>41.81</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="1">
         <v>0.20899999999999999</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="1">
         <v>0.52900000000000003</v>
       </c>
-      <c r="M7" s="3">
+      <c r="O7" s="2">
         <v>83.03</v>
       </c>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="7">
+      <c r="S7" s="16"/>
+      <c r="T7">
         <v>0</v>
       </c>
-      <c r="S7" s="7">
+      <c r="U7">
         <v>0</v>
       </c>
-      <c r="T7" s="7">
+      <c r="V7">
         <v>0</v>
       </c>
-      <c r="U7" s="8">
+      <c r="W7" s="25">
         <v>0</v>
       </c>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="7">
+      <c r="X7" s="25">
         <v>0</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Y7" s="6">
         <v>0</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AC7" s="16"/>
+      <c r="AD7">
         <v>0</v>
       </c>
-      <c r="AB7" s="8">
+      <c r="AE7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C8" s="20" t="s">
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="25">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="19" t="s">
+      <c r="H8" s="21">
+        <v>95.57</v>
+      </c>
+      <c r="I8" s="2">
+        <v>41.81</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="K8" s="2">
+      <c r="M8" s="1">
         <v>0.20899999999999999</v>
       </c>
-      <c r="L8" s="2">
+      <c r="N8" s="1">
         <v>0.54200000000000004</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="2">
         <v>83.03</v>
       </c>
-      <c r="Q8" s="20" t="s">
+      <c r="S8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="R8" s="7">
+      <c r="T8">
         <v>0.60099999999999998</v>
       </c>
-      <c r="S8" s="7">
+      <c r="U8">
         <v>0.86299999999999999</v>
       </c>
-      <c r="T8" s="7">
+      <c r="V8">
         <v>0.254</v>
       </c>
-      <c r="U8" s="8">
+      <c r="W8" s="25">
         <v>73.540000000000006</v>
       </c>
-      <c r="X8" s="20" t="s">
+      <c r="X8" s="21">
+        <v>95.45</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>46.27</v>
+      </c>
+      <c r="AC8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="AD8">
         <v>0.61299999999999999</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="AE8">
         <v>0.871</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AF8">
         <v>0.29299999999999998</v>
       </c>
-      <c r="AB8" s="8">
+      <c r="AG8" s="25">
         <v>79.040000000000006</v>
       </c>
-    </row>
-    <row r="9" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C9" s="20" t="s">
+      <c r="AH8" s="21">
+        <v>96.29</v>
+      </c>
+      <c r="AI8" s="2">
+        <v>57.58</v>
+      </c>
+    </row>
+    <row r="9" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="19" t="s">
+      <c r="H9" s="21">
+        <v>94.13</v>
+      </c>
+      <c r="I9" s="2">
+        <v>45.53</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="2">
+      <c r="M9" s="1">
         <v>0.184</v>
       </c>
-      <c r="L9" s="2">
+      <c r="N9" s="1">
         <v>0.44</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="2">
         <v>79.459999999999994</v>
       </c>
-      <c r="Q9" s="20" t="s">
+      <c r="S9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="R9" s="7">
+      <c r="T9">
         <v>0.59199999999999997</v>
       </c>
-      <c r="S9" s="7">
+      <c r="U9">
         <v>0.86599999999999999</v>
       </c>
-      <c r="T9" s="7">
+      <c r="V9">
         <v>0.27200000000000002</v>
       </c>
-      <c r="U9" s="8">
+      <c r="W9" s="25">
         <v>74.73</v>
       </c>
-      <c r="X9" s="20" t="s">
+      <c r="X9" s="21">
+        <v>95.45</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>48.95</v>
+      </c>
+      <c r="AC9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="AD9">
         <v>0.62</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="AE9">
         <v>0.872</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AF9">
         <v>0.307</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AG9" s="25">
         <v>80.959999999999994</v>
       </c>
-    </row>
-    <row r="10" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C10" s="14" t="s">
+      <c r="AH9" s="21">
+        <v>96.88</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>61.16</v>
+      </c>
+    </row>
+    <row r="10" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="21" t="s">
+      <c r="H10" s="3">
+        <v>65.069999999999993</v>
+      </c>
+      <c r="I10" s="4">
+        <v>15.17</v>
+      </c>
+      <c r="L10" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K10" s="4">
+      <c r="M10" s="3">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="L10" s="4">
+      <c r="N10" s="3">
         <v>0.245</v>
       </c>
-      <c r="M10" s="5">
+      <c r="O10" s="4">
         <v>35.71</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="S10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="R10" s="9">
+      <c r="T10" s="7">
         <v>0.42699999999999999</v>
       </c>
-      <c r="S10" s="9">
+      <c r="U10" s="7">
         <v>0.66400000000000003</v>
       </c>
-      <c r="T10" s="9">
+      <c r="V10" s="7">
         <v>0.13200000000000001</v>
       </c>
-      <c r="U10" s="10">
+      <c r="W10" s="7">
         <v>45.82</v>
       </c>
-      <c r="X10" s="14" t="s">
+      <c r="X10" s="3">
+        <v>68.77</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="AC10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="Y10" s="9">
+      <c r="AD10" s="7">
         <v>0.48599999999999999</v>
       </c>
-      <c r="Z10" s="9">
+      <c r="AE10" s="7">
         <v>0.74099999999999999</v>
       </c>
-      <c r="AA10" s="9">
+      <c r="AF10" s="7">
         <v>0.16800000000000001</v>
       </c>
-      <c r="AB10" s="10">
+      <c r="AG10" s="7">
         <v>54.04</v>
       </c>
-    </row>
-    <row r="11" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="AH10" s="3">
+        <v>78.58</v>
+      </c>
+      <c r="AI10" s="4">
+        <v>23.51</v>
+      </c>
+    </row>
+    <row r="11" spans="3:35" x14ac:dyDescent="0.35">
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C12" s="6" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C12" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="1"/>
@@ -1305,1269 +1499,1461 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="16" t="s">
+      <c r="L12" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C13" s="13"/>
-      <c r="D13" s="13" t="s">
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15" t="s">
+      <c r="H13" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="N13" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="M13" s="15" t="s">
+      <c r="O13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="S13" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="AC13" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C14" s="22" t="s">
+    <row r="14" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="18" t="s">
+      <c r="H14" s="21">
+        <v>98.56</v>
+      </c>
+      <c r="I14" s="2">
+        <v>63.69</v>
+      </c>
+      <c r="L14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="2">
+      <c r="M14" s="1">
         <v>0.39900000000000002</v>
       </c>
-      <c r="L14" s="2">
+      <c r="N14" s="1">
         <v>0.74199999999999999</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="2">
         <v>92.85</v>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13" t="s">
+      <c r="S14" s="10"/>
+      <c r="T14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="S14" s="13" t="s">
+      <c r="U14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="T14" s="13" t="s">
+      <c r="V14" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="U14" s="13" t="s">
+      <c r="W14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13" t="s">
+      <c r="X14" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y14" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="Z14" s="13" t="s">
+      <c r="AE14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AA14" s="13" t="s">
+      <c r="AF14" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AB14" s="13" t="s">
+      <c r="AG14" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C15" s="20" t="s">
+      <c r="AH14" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI14" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C15" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="19" t="s">
+      <c r="H15" s="21">
+        <v>98.44</v>
+      </c>
+      <c r="I15" s="2">
+        <v>64.13</v>
+      </c>
+      <c r="L15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="2">
+      <c r="M15" s="1">
         <v>0.375</v>
       </c>
-      <c r="L15" s="2">
+      <c r="N15" s="1">
         <v>0.749</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="2">
         <v>92.85</v>
       </c>
-      <c r="Q15" s="20" t="s">
+      <c r="S15" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R15" s="7">
-        <f>R4-D4</f>
+      <c r="T15">
+        <f>T4-D4</f>
         <v>4.3000000000000038E-2</v>
       </c>
-      <c r="S15" s="7">
-        <f>S4-E4</f>
+      <c r="U15">
+        <f>U4-E4</f>
         <v>3.5000000000000031E-2</v>
       </c>
-      <c r="T15" s="7">
-        <f>T4-F4</f>
+      <c r="V15">
+        <f>V4-F4</f>
         <v>5.4999999999999966E-2</v>
       </c>
-      <c r="U15" s="8">
-        <f>U4-G4</f>
+      <c r="W15" s="24">
+        <f>W4-G4</f>
         <v>1.5900000000000034</v>
       </c>
-      <c r="X15" s="20" t="s">
+      <c r="X15" s="21"/>
+      <c r="Y15" s="2"/>
+      <c r="AC15" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="Y15" s="7">
-        <f>Y4-D4</f>
+      <c r="AD15">
+        <f>AD4-D4</f>
         <v>5.600000000000005E-2</v>
       </c>
-      <c r="Z15" s="7">
-        <f>Z4-E4</f>
+      <c r="AE15">
+        <f>AE4-E4</f>
         <v>3.9000000000000035E-2</v>
       </c>
-      <c r="AA15" s="7">
-        <f>AA4-F4</f>
+      <c r="AF15">
+        <f>AF4-F4</f>
         <v>7.6999999999999985E-2</v>
       </c>
-      <c r="AB15" s="8">
-        <f>AB4-G4</f>
+      <c r="AG15" s="24">
+        <f>AG4-G4</f>
         <v>6.0300000000000011</v>
       </c>
-    </row>
-    <row r="16" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C16" s="20" t="s">
+      <c r="AH15" s="21"/>
+      <c r="AI15" s="2"/>
+    </row>
+    <row r="16" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>0.35299999999999998</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="19" t="s">
+      <c r="H16" s="21">
+        <v>98.56</v>
+      </c>
+      <c r="I16" s="2">
+        <v>64.28</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="2">
+      <c r="M16" s="1">
         <v>0.35299999999999998</v>
       </c>
-      <c r="L16" s="2">
+      <c r="N16" s="1">
         <v>0.754</v>
       </c>
-      <c r="M16" s="3">
+      <c r="O16" s="2">
         <v>91.96</v>
       </c>
-      <c r="Q16" s="20" t="s">
+      <c r="S16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="R16" s="7">
-        <f>R5-D5</f>
+      <c r="T16">
+        <f>T5-D5</f>
         <v>4.7999999999999932E-2</v>
       </c>
-      <c r="S16" s="7">
-        <f>S5-E5</f>
+      <c r="U16">
+        <f>U5-E5</f>
         <v>4.7000000000000042E-2</v>
       </c>
-      <c r="T16" s="7">
-        <f>T5-F5</f>
+      <c r="V16">
+        <f>V5-F5</f>
         <v>4.9000000000000016E-2</v>
       </c>
-      <c r="U16" s="8">
-        <f>U5-G5</f>
+      <c r="W16" s="25">
+        <f>W5-G5</f>
         <v>1.0600000000000023</v>
       </c>
-      <c r="X16" s="20" t="s">
+      <c r="X16" s="21"/>
+      <c r="Y16" s="2"/>
+      <c r="AC16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="Y16" s="7">
-        <f>Y5-D5</f>
+      <c r="AD16">
+        <f>AD5-D5</f>
         <v>6.2999999999999945E-2</v>
       </c>
-      <c r="Z16" s="7">
-        <f>Z5-E5</f>
+      <c r="AE16">
+        <f>AE5-E5</f>
         <v>5.1000000000000045E-2</v>
       </c>
-      <c r="AA16" s="7">
-        <f>AA5-F5</f>
+      <c r="AF16">
+        <f>AF5-F5</f>
         <v>7.7999999999999986E-2</v>
       </c>
-      <c r="AB16" s="8">
-        <f>AB5-G5</f>
+      <c r="AG16" s="25">
+        <f>AG5-G5</f>
         <v>6.230000000000004</v>
       </c>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C17" s="20" t="s">
+      <c r="AH16" s="21"/>
+      <c r="AI16" s="2"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>0.308</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="19" t="s">
+      <c r="H17" s="21">
+        <v>97.96</v>
+      </c>
+      <c r="I17" s="2">
+        <v>55.5</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="2">
+      <c r="M17" s="1">
         <v>0.308</v>
       </c>
-      <c r="L17" s="2">
+      <c r="N17" s="1">
         <v>0.71699999999999997</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="2">
         <v>89.28</v>
       </c>
-      <c r="Q17" s="20" t="s">
+      <c r="S17" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="R17" s="7">
-        <f>R8-D8</f>
+      <c r="T17">
+        <f>T8-D8</f>
         <v>6.899999999999995E-2</v>
       </c>
-      <c r="S17" s="7">
-        <f>S8-E8</f>
+      <c r="U17">
+        <f>U8-E8</f>
         <v>6.9999999999999951E-2</v>
       </c>
-      <c r="T17" s="7">
-        <f>T8-F8</f>
+      <c r="V17">
+        <f>V8-F8</f>
         <v>4.5000000000000012E-2</v>
       </c>
-      <c r="U17" s="8">
-        <f>U8-G8</f>
+      <c r="W17" s="25">
+        <f>W8-G8</f>
         <v>1.9200000000000017</v>
       </c>
-      <c r="X17" s="20" t="s">
+      <c r="X17" s="21"/>
+      <c r="Y17" s="2"/>
+      <c r="AC17" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="Y17" s="7">
-        <f>Y8-D8</f>
+      <c r="AD17">
+        <f>AD8-D8</f>
         <v>8.0999999999999961E-2</v>
       </c>
-      <c r="Z17" s="7">
-        <f>Z8-E8</f>
+      <c r="AE17">
+        <f>AE8-E8</f>
         <v>7.7999999999999958E-2</v>
       </c>
-      <c r="AA17" s="7">
-        <f>AA8-F8</f>
+      <c r="AF17">
+        <f>AF8-F8</f>
         <v>8.3999999999999991E-2</v>
       </c>
-      <c r="AB17" s="8">
-        <f>AB8-G8</f>
+      <c r="AG17" s="25">
+        <f>AG8-G8</f>
         <v>7.4200000000000017</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C18" s="20" t="s">
+      <c r="AH17" s="21"/>
+      <c r="AI17" s="2"/>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C18" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="19" t="s">
+      <c r="H18" s="21">
+        <v>97.96</v>
+      </c>
+      <c r="I18" s="2">
+        <v>56.99</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="K18" s="2">
+      <c r="M18" s="1">
         <v>0.33400000000000002</v>
       </c>
-      <c r="L18" s="2">
+      <c r="N18" s="1">
         <v>0.74299999999999999</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="2">
         <v>91.07</v>
       </c>
-      <c r="Q18" s="20" t="s">
+      <c r="S18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="R18" s="7">
-        <f>R9-D9</f>
+      <c r="T18">
+        <f>T9-D9</f>
         <v>0.11599999999999999</v>
       </c>
-      <c r="S18" s="7">
-        <f>S9-E9</f>
+      <c r="U18">
+        <f>U9-E9</f>
         <v>0.15400000000000003</v>
       </c>
-      <c r="T18" s="7">
-        <f>T9-F9</f>
+      <c r="V18">
+        <f>V9-F9</f>
         <v>8.8000000000000023E-2</v>
       </c>
-      <c r="U18" s="8">
-        <f>U9-G9</f>
+      <c r="W18" s="25">
+        <f>W9-G9</f>
         <v>2.3200000000000074</v>
       </c>
-      <c r="X18" s="20" t="s">
+      <c r="X18" s="21"/>
+      <c r="Y18" s="2"/>
+      <c r="AC18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="Y18" s="7">
-        <f>Y9-D9</f>
+      <c r="AD18">
+        <f>AD9-D9</f>
         <v>0.14400000000000002</v>
       </c>
-      <c r="Z18" s="7">
-        <f>Z9-E9</f>
+      <c r="AE18">
+        <f>AE9-E9</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="AA18" s="7">
-        <f>AA9-F9</f>
+      <c r="AF18">
+        <f>AF9-F9</f>
         <v>0.123</v>
       </c>
-      <c r="AB18" s="8">
-        <f>AB9-G9</f>
+      <c r="AG18" s="25">
+        <f>AG9-G9</f>
         <v>8.5499999999999972</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C19" s="20" t="s">
+      <c r="AH18" s="21"/>
+      <c r="AI18" s="2"/>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C19" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="19" t="s">
+      <c r="H19" s="21">
+        <v>98.56</v>
+      </c>
+      <c r="I19" s="2">
+        <v>62.64</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="K19" s="2">
+      <c r="M19" s="1">
         <v>0.36299999999999999</v>
       </c>
-      <c r="L19" s="2">
+      <c r="N19" s="1">
         <v>0.72499999999999998</v>
       </c>
-      <c r="M19" s="3">
+      <c r="O19" s="2">
         <v>91.96</v>
       </c>
-      <c r="Q19" s="20" t="s">
+      <c r="S19" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="R19" s="7">
-        <f>R10-D10</f>
+      <c r="T19">
+        <f>T10-D10</f>
         <v>0.14699999999999996</v>
       </c>
-      <c r="S19" s="7">
-        <f>S10-E10</f>
+      <c r="U19">
+        <f>U10-E10</f>
         <v>0.22600000000000003</v>
       </c>
-      <c r="T19" s="7">
-        <f>T10-F10</f>
+      <c r="V19">
+        <f>V10-F10</f>
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="U19" s="8">
-        <f>U10-G10</f>
+      <c r="W19" s="7">
+        <f>W10-G10</f>
         <v>2.990000000000002</v>
       </c>
-      <c r="X19" s="20" t="s">
+      <c r="X19" s="21"/>
+      <c r="Y19" s="2"/>
+      <c r="AC19" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="Y19" s="7">
-        <f>Y10-D10</f>
+      <c r="AD19">
+        <f>AD10-D10</f>
         <v>0.20599999999999996</v>
       </c>
-      <c r="Z19" s="7">
-        <f>Z10-E10</f>
+      <c r="AE19">
+        <f>AE10-E10</f>
         <v>0.30299999999999999</v>
       </c>
-      <c r="AA19" s="7">
-        <f>AA10-F10</f>
+      <c r="AF19">
+        <f>AF10-F10</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="AB19" s="8">
-        <f>AB10-G10</f>
+      <c r="AG19" s="7">
+        <f>AG10-G10</f>
         <v>11.21</v>
       </c>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C20" s="14" t="s">
+      <c r="AH19" s="21"/>
+      <c r="AI19" s="2"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="21" t="s">
+      <c r="H20" s="3">
+        <v>77.87</v>
+      </c>
+      <c r="I20" s="4">
+        <v>22.91</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K20" s="4">
+      <c r="M20" s="3">
         <v>0.113</v>
       </c>
-      <c r="L20" s="4">
+      <c r="N20" s="3">
         <v>0.30099999999999999</v>
       </c>
-      <c r="M20" s="5">
+      <c r="O20" s="4">
         <v>42.85</v>
       </c>
-      <c r="Q20" s="13" t="s">
+      <c r="S20" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="R20" s="11">
-        <f>AVERAGEA(R15:R19)</f>
+      <c r="T20" s="8">
+        <f>AVERAGEA(T15:T19)</f>
         <v>8.4599999999999981E-2</v>
       </c>
-      <c r="S20" s="11">
-        <f t="shared" ref="S20:U20" si="0">AVERAGEA(S15:S19)</f>
+      <c r="U20" s="8">
+        <f t="shared" ref="U20:W20" si="0">AVERAGEA(U15:U19)</f>
         <v>0.10640000000000001</v>
       </c>
-      <c r="T20" s="11">
+      <c r="V20" s="8">
         <f t="shared" si="0"/>
         <v>5.7200000000000008E-2</v>
       </c>
-      <c r="U20" s="12">
+      <c r="W20" s="8">
         <f t="shared" si="0"/>
         <v>1.9760000000000033</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="X20" s="26"/>
+      <c r="Y20" s="22"/>
+      <c r="AC20" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="Y20" s="11">
-        <f>AVERAGEA(Y15:Y19)</f>
+      <c r="AD20" s="8">
+        <f>AVERAGEA(AD15:AD19)</f>
         <v>0.10999999999999999</v>
       </c>
-      <c r="Z20" s="11">
-        <f t="shared" ref="Z20:AA20" si="1">AVERAGEA(Z15:Z19)</f>
+      <c r="AE20" s="8">
+        <f t="shared" ref="AE20:AF20" si="1">AVERAGEA(AE15:AE19)</f>
         <v>0.12620000000000001</v>
       </c>
-      <c r="AA20" s="11">
+      <c r="AF20" s="8">
         <f t="shared" si="1"/>
         <v>8.9400000000000007E-2</v>
       </c>
-      <c r="AB20" s="12">
-        <f>AVERAGEA(AB15:AB19)</f>
+      <c r="AG20" s="9">
+        <f>AVERAGEA(AG15:AG19)</f>
         <v>7.8880000000000008</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.35">
+      <c r="AH20" s="23"/>
+      <c r="AI20" s="22"/>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.35">
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C22" s="6" t="s">
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="X21" s="21"/>
+      <c r="Y21" s="21"/>
+      <c r="AH21" s="21"/>
+      <c r="AI21" s="21"/>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C22" s="5" t="s">
         <v>69</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="17" t="s">
+      <c r="L22" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="X22" s="23" t="s">
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C23" s="10"/>
+      <c r="D23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC23" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C23" s="13"/>
-      <c r="D23" s="15" t="s">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C24" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" ref="D24:I30" si="2">D14-D4</f>
+        <v>0.1090000000000001</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="2"/>
+        <v>9.2000000000000082E-2</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="2"/>
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="G24" s="27">
+        <f t="shared" si="2"/>
+        <v>7.3599999999999994</v>
+      </c>
+      <c r="H24" s="1">
+        <f>H14-H4</f>
+        <v>2.1500000000000057</v>
+      </c>
+      <c r="I24" s="19">
+        <f>I14-I4</f>
+        <v>13.989999999999995</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" ref="M24:O30" si="3">M14-M4</f>
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="N24" s="1">
+        <f t="shared" si="3"/>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="O24" s="2">
+        <f t="shared" si="3"/>
+        <v>5.3499999999999943</v>
+      </c>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U24" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V24" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="W24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X24" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y24" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC24" s="10"/>
+      <c r="AD24" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE24" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF24" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH24" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI24" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C25" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="2"/>
+        <v>0.11699999999999999</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="2"/>
+        <v>0.1070000000000001</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="2"/>
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="2"/>
+        <v>7.4900000000000091</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999915</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="2"/>
+        <v>15.179999999999993</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="3"/>
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="N25" s="1">
+        <f t="shared" si="3"/>
+        <v>0.19399999999999995</v>
+      </c>
+      <c r="O25" s="2">
+        <f t="shared" si="3"/>
+        <v>5.3499999999999943</v>
+      </c>
+      <c r="S25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="T25">
+        <f>T4-D14</f>
+        <v>-6.6000000000000059E-2</v>
+      </c>
+      <c r="U25">
+        <f>U4-E14</f>
+        <v>-5.7000000000000051E-2</v>
+      </c>
+      <c r="V25">
+        <f>V4-F14</f>
+        <v>-0.11400000000000005</v>
+      </c>
+      <c r="W25" s="24">
+        <f>W4-G14</f>
+        <v>-5.769999999999996</v>
+      </c>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="2"/>
+      <c r="AC25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD25">
+        <f>AD4-D14</f>
+        <v>-5.3000000000000047E-2</v>
+      </c>
+      <c r="AE25">
+        <f>AE4-E14</f>
+        <v>-5.3000000000000047E-2</v>
+      </c>
+      <c r="AF25">
+        <f>AF4-F14</f>
+        <v>-9.2000000000000026E-2</v>
+      </c>
+      <c r="AG25" s="6">
+        <f>AG4-G14</f>
+        <v>-1.3299999999999983</v>
+      </c>
+      <c r="AH25" s="20"/>
+      <c r="AI25" s="2"/>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="2"/>
+        <v>0.14300000000000002</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="2"/>
+        <v>0.14500000000000002</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="2"/>
+        <v>0.15499999999999997</v>
+      </c>
+      <c r="G26" s="21">
+        <f t="shared" si="2"/>
+        <v>8.8100000000000023</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="2"/>
+        <v>2.6299999999999955</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="2"/>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="3"/>
+        <v>0.15499999999999997</v>
+      </c>
+      <c r="N26" s="1">
+        <f t="shared" si="3"/>
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="3"/>
+        <v>12.5</v>
+      </c>
+      <c r="S26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="T26">
+        <f>T5-D15</f>
+        <v>-6.9000000000000061E-2</v>
+      </c>
+      <c r="U26">
+        <f>U5-E15</f>
+        <v>-6.0000000000000053E-2</v>
+      </c>
+      <c r="V26">
+        <f>V5-F15</f>
+        <v>-9.4999999999999973E-2</v>
+      </c>
+      <c r="W26" s="25">
+        <f>W5-G15</f>
+        <v>-6.4300000000000068</v>
+      </c>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="2"/>
+      <c r="AC26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD26">
+        <f>AD5-D15</f>
+        <v>-5.4000000000000048E-2</v>
+      </c>
+      <c r="AE26">
+        <f>AE5-E15</f>
+        <v>-5.600000000000005E-2</v>
+      </c>
+      <c r="AF26">
+        <f>AF5-F15</f>
+        <v>-6.6000000000000003E-2</v>
+      </c>
+      <c r="AG26" s="6">
+        <f>AG5-G15</f>
+        <v>-1.2600000000000051</v>
+      </c>
+      <c r="AH26" s="20"/>
+      <c r="AI26" s="2"/>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="2"/>
+        <v>0.10599999999999998</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="2"/>
+        <v>0.10199999999999998</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="2"/>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="2"/>
+        <v>7.3599999999999994</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="2"/>
+        <v>2.269999999999996</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="2"/>
+        <v>13.689999999999998</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" si="3"/>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="N27" s="1">
+        <f t="shared" si="3"/>
+        <v>0.18799999999999994</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="3"/>
+        <v>6.25</v>
+      </c>
+      <c r="S27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="T27">
+        <f>T8-D18</f>
+        <v>-4.7000000000000042E-2</v>
+      </c>
+      <c r="U27">
+        <f>U8-E18</f>
+        <v>-3.8000000000000034E-2</v>
+      </c>
+      <c r="V27">
+        <f>V8-F18</f>
+        <v>-8.0000000000000016E-2</v>
+      </c>
+      <c r="W27" s="25">
+        <f>W8-G18</f>
+        <v>-6.1599999999999966</v>
+      </c>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="2"/>
+      <c r="AC27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD27">
+        <f>AD8-D18</f>
+        <v>-3.5000000000000031E-2</v>
+      </c>
+      <c r="AE27">
+        <f>AE8-E18</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="AF27">
+        <f>AF8-F18</f>
+        <v>-4.1000000000000036E-2</v>
+      </c>
+      <c r="AG27" s="6">
+        <f>AG8-G18</f>
+        <v>-0.65999999999999659</v>
+      </c>
+      <c r="AH27" s="20"/>
+      <c r="AI27" s="2"/>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="2"/>
+        <v>0.11599999999999999</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="2"/>
+        <v>0.10799999999999998</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="2"/>
+        <v>0.12500000000000003</v>
+      </c>
+      <c r="G28" s="21">
+        <f t="shared" si="2"/>
+        <v>8.0799999999999983</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="2"/>
+        <v>2.3900000000000006</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="2"/>
+        <v>15.18</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="3"/>
+        <v>0.12500000000000003</v>
+      </c>
+      <c r="N28" s="1">
+        <f t="shared" si="3"/>
+        <v>0.20099999999999996</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" si="3"/>
+        <v>8.039999999999992</v>
+      </c>
+      <c r="S28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="T28">
+        <f>T9-D19</f>
+        <v>-6.800000000000006E-2</v>
+      </c>
+      <c r="U28">
+        <f>U9-E19</f>
+        <v>-3.3000000000000029E-2</v>
+      </c>
+      <c r="V28">
+        <f>V9-F19</f>
+        <v>-9.099999999999997E-2</v>
+      </c>
+      <c r="W28" s="25">
+        <f>W9-G19</f>
+        <v>-7.8199999999999932</v>
+      </c>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="2"/>
+      <c r="AC28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD28">
+        <f>AD9-D19</f>
+        <v>-4.0000000000000036E-2</v>
+      </c>
+      <c r="AE28">
+        <f>AE9-E19</f>
+        <v>-2.7000000000000024E-2</v>
+      </c>
+      <c r="AF28">
+        <f>AF9-F19</f>
+        <v>-5.5999999999999994E-2</v>
+      </c>
+      <c r="AG28" s="6">
+        <f>AG9-G19</f>
+        <v>-1.5900000000000034</v>
+      </c>
+      <c r="AH28" s="20"/>
+      <c r="AI28" s="2"/>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="2"/>
+        <v>0.18400000000000005</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="2"/>
+        <v>0.18700000000000006</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="2"/>
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="2"/>
+        <v>10.14</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="2"/>
+        <v>4.4300000000000068</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="2"/>
+        <v>17.11</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="3"/>
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="N29" s="1">
+        <f t="shared" si="3"/>
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="O29" s="2">
+        <f t="shared" si="3"/>
+        <v>12.5</v>
+      </c>
+      <c r="S29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="T29">
+        <f>T10-D20</f>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="U29">
+        <f>U10-E20</f>
+        <v>9.4000000000000083E-2</v>
+      </c>
+      <c r="V29">
+        <f>V10-F20</f>
+        <v>1.9000000000000003E-2</v>
+      </c>
+      <c r="W29" s="25">
+        <f>W10-G20</f>
+        <v>-7.5600000000000023</v>
+      </c>
+      <c r="X29" s="21"/>
+      <c r="Y29" s="2"/>
+      <c r="AC29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD29">
+        <f>AD10-D20</f>
+        <v>0.12</v>
+      </c>
+      <c r="AE29">
+        <f>AE10-E20</f>
+        <v>0.17100000000000004</v>
+      </c>
+      <c r="AF29">
+        <f>AF10-F20</f>
+        <v>5.5000000000000007E-2</v>
+      </c>
+      <c r="AG29" s="6">
+        <f>AG10-G20</f>
+        <v>0.65999999999999659</v>
+      </c>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="2"/>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="2"/>
+        <v>8.5999999999999965E-2</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="2"/>
+        <v>0.13199999999999995</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="G30" s="21">
+        <f t="shared" si="2"/>
+        <v>10.550000000000004</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="2"/>
+        <v>12.800000000000011</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="2"/>
+        <v>7.74</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="3"/>
+        <v>0.03</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="3"/>
+        <v>5.5999999999999994E-2</v>
+      </c>
+      <c r="O30" s="2">
+        <f t="shared" si="3"/>
+        <v>7.1400000000000006</v>
+      </c>
+      <c r="S30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="T30" s="8">
+        <f>AVERAGEA(T25:T29)</f>
+        <v>-3.7800000000000042E-2</v>
+      </c>
+      <c r="U30" s="8">
+        <f t="shared" ref="U30:W30" si="4">AVERAGEA(U25:U29)</f>
+        <v>-1.8800000000000018E-2</v>
+      </c>
+      <c r="V30" s="8">
+        <f t="shared" si="4"/>
+        <v>-7.22E-2</v>
+      </c>
+      <c r="W30" s="8">
+        <f t="shared" si="4"/>
+        <v>-6.7479999999999993</v>
+      </c>
+      <c r="X30" s="26"/>
+      <c r="Y30" s="22"/>
+      <c r="AC30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z23" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA23" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB23" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C24" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="2">
-        <f>D14-D4</f>
-        <v>0.1090000000000001</v>
-      </c>
-      <c r="E24" s="2">
-        <f>E14-E4</f>
-        <v>9.2000000000000082E-2</v>
-      </c>
-      <c r="F24" s="2">
-        <f>F14-F4</f>
-        <v>0.16900000000000001</v>
-      </c>
-      <c r="G24" s="3">
-        <f>G14-G4</f>
-        <v>7.3599999999999994</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K24" s="2">
-        <f>K14-K4</f>
-        <v>0.16900000000000001</v>
-      </c>
-      <c r="L24" s="2">
-        <f>L14-L4</f>
-        <v>0.16000000000000003</v>
-      </c>
-      <c r="M24" s="3">
-        <f>M14-M4</f>
-        <v>5.3499999999999943</v>
-      </c>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="S24" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="T24" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="U24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="X24" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y24" s="7">
-        <f>Y4-D14</f>
-        <v>-5.3000000000000047E-2</v>
-      </c>
-      <c r="Z24" s="7">
-        <f>Z4-E14</f>
-        <v>-5.3000000000000047E-2</v>
-      </c>
-      <c r="AA24" s="7">
-        <f>AA4-F14</f>
-        <v>-9.2000000000000026E-2</v>
-      </c>
-      <c r="AB24" s="8">
-        <f>AB4-G14</f>
-        <v>-1.3299999999999983</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C25" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="2">
-        <f>D15-D5</f>
-        <v>0.11699999999999999</v>
-      </c>
-      <c r="E25" s="2">
-        <f>E15-E5</f>
-        <v>0.1070000000000001</v>
-      </c>
-      <c r="F25" s="2">
-        <f>F15-F5</f>
-        <v>0.14399999999999999</v>
-      </c>
-      <c r="G25" s="3">
-        <f>G15-G5</f>
-        <v>7.4900000000000091</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="K25" s="2">
-        <f>K15-K5</f>
-        <v>0.14399999999999999</v>
-      </c>
-      <c r="L25" s="2">
-        <f>L15-L5</f>
-        <v>0.19399999999999995</v>
-      </c>
-      <c r="M25" s="3">
-        <f>M15-M5</f>
-        <v>5.3499999999999943</v>
-      </c>
-      <c r="Q25" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="R25" s="7">
-        <f t="shared" ref="R25:U26" si="2">R4-D14</f>
-        <v>-6.6000000000000059E-2</v>
-      </c>
-      <c r="S25" s="7">
-        <f t="shared" si="2"/>
-        <v>-5.7000000000000051E-2</v>
-      </c>
-      <c r="T25" s="7">
-        <f t="shared" si="2"/>
-        <v>-0.11400000000000005</v>
-      </c>
-      <c r="U25" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.769999999999996</v>
-      </c>
-      <c r="X25" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y25" s="7">
-        <f>Y5-D15</f>
-        <v>-5.4000000000000048E-2</v>
-      </c>
-      <c r="Z25" s="7">
-        <f>Z5-E15</f>
-        <v>-5.600000000000005E-2</v>
-      </c>
-      <c r="AA25" s="7">
-        <f>AA5-F15</f>
-        <v>-6.6000000000000003E-2</v>
-      </c>
-      <c r="AB25" s="8">
-        <f>AB5-G15</f>
-        <v>-1.2600000000000051</v>
-      </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C26" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="2">
-        <f>D16-D6</f>
-        <v>0.14300000000000002</v>
-      </c>
-      <c r="E26" s="2">
-        <f>E16-E6</f>
-        <v>0.14500000000000002</v>
-      </c>
-      <c r="F26" s="2">
-        <f>F16-F6</f>
-        <v>0.15499999999999997</v>
-      </c>
-      <c r="G26" s="3">
-        <f>G16-G6</f>
-        <v>8.8100000000000023</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" s="2">
-        <f>K16-K6</f>
-        <v>0.15499999999999997</v>
-      </c>
-      <c r="L26" s="2">
-        <f>L16-L6</f>
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="M26" s="3">
-        <f>M16-M6</f>
-        <v>12.5</v>
-      </c>
-      <c r="Q26" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="7">
-        <f t="shared" si="2"/>
-        <v>-6.9000000000000061E-2</v>
-      </c>
-      <c r="S26" s="7">
-        <f t="shared" si="2"/>
-        <v>-6.0000000000000053E-2</v>
-      </c>
-      <c r="T26" s="7">
-        <f t="shared" si="2"/>
-        <v>-9.4999999999999973E-2</v>
-      </c>
-      <c r="U26" s="8">
-        <f t="shared" si="2"/>
-        <v>-6.4300000000000068</v>
-      </c>
-      <c r="X26" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y26" s="7">
-        <f>Y8-D18</f>
-        <v>-3.5000000000000031E-2</v>
-      </c>
-      <c r="Z26" s="7">
-        <f>Z8-E18</f>
-        <v>-3.0000000000000027E-2</v>
-      </c>
-      <c r="AA26" s="7">
-        <f>AA8-F18</f>
-        <v>-4.1000000000000036E-2</v>
-      </c>
-      <c r="AB26" s="8">
-        <f>AB8-G18</f>
-        <v>-0.65999999999999659</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C27" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="2">
-        <f>D17-D7</f>
-        <v>0.10599999999999998</v>
-      </c>
-      <c r="E27" s="2">
-        <f>E17-E7</f>
-        <v>0.10199999999999998</v>
-      </c>
-      <c r="F27" s="2">
-        <f>F17-F7</f>
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="G27" s="3">
-        <f>G17-G7</f>
-        <v>7.3599999999999994</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="K27" s="2">
-        <f>K17-K7</f>
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="L27" s="2">
-        <f>L17-L7</f>
-        <v>0.18799999999999994</v>
-      </c>
-      <c r="M27" s="3">
-        <f>M17-M7</f>
-        <v>6.25</v>
-      </c>
-      <c r="Q27" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="R27" s="7">
-        <f t="shared" ref="R27:R29" si="3">R8-D18</f>
-        <v>-4.7000000000000042E-2</v>
-      </c>
-      <c r="S27" s="7">
-        <f t="shared" ref="S27:U29" si="4">S8-E18</f>
-        <v>-3.8000000000000034E-2</v>
-      </c>
-      <c r="T27" s="7">
-        <f t="shared" si="4"/>
-        <v>-8.0000000000000016E-2</v>
-      </c>
-      <c r="U27" s="8">
-        <f t="shared" si="4"/>
-        <v>-6.1599999999999966</v>
-      </c>
-      <c r="X27" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y27" s="7">
-        <f>Y9-D19</f>
-        <v>-4.0000000000000036E-2</v>
-      </c>
-      <c r="Z27" s="7">
-        <f>Z9-E19</f>
-        <v>-2.7000000000000024E-2</v>
-      </c>
-      <c r="AA27" s="7">
-        <f>AA9-F19</f>
-        <v>-5.5999999999999994E-2</v>
-      </c>
-      <c r="AB27" s="8">
-        <f>AB9-G19</f>
-        <v>-1.5900000000000034</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C28" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="2">
-        <f>D18-D8</f>
-        <v>0.11599999999999999</v>
-      </c>
-      <c r="E28" s="2">
-        <f>E18-E8</f>
-        <v>0.10799999999999998</v>
-      </c>
-      <c r="F28" s="2">
-        <f>F18-F8</f>
-        <v>0.12500000000000003</v>
-      </c>
-      <c r="G28" s="3">
-        <f>G18-G8</f>
-        <v>8.0799999999999983</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="2">
-        <f>K18-K8</f>
-        <v>0.12500000000000003</v>
-      </c>
-      <c r="L28" s="2">
-        <f>L18-L8</f>
-        <v>0.20099999999999996</v>
-      </c>
-      <c r="M28" s="3">
-        <f>M18-M8</f>
-        <v>8.039999999999992</v>
-      </c>
-      <c r="Q28" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="R28" s="7">
-        <f t="shared" si="3"/>
-        <v>-6.800000000000006E-2</v>
-      </c>
-      <c r="S28" s="7">
-        <f t="shared" si="4"/>
-        <v>-3.3000000000000029E-2</v>
-      </c>
-      <c r="T28" s="7">
-        <f t="shared" si="4"/>
-        <v>-9.099999999999997E-2</v>
-      </c>
-      <c r="U28" s="8">
-        <f t="shared" si="4"/>
-        <v>-7.8199999999999932</v>
-      </c>
-      <c r="X28" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y28" s="7">
-        <f>Y10-D20</f>
-        <v>0.12</v>
-      </c>
-      <c r="Z28" s="7">
-        <f>Z10-E20</f>
-        <v>0.17100000000000004</v>
-      </c>
-      <c r="AA28" s="7">
-        <f>AA10-F20</f>
-        <v>5.5000000000000007E-2</v>
-      </c>
-      <c r="AB28" s="8">
-        <f>AB10-G20</f>
-        <v>0.65999999999999659</v>
-      </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C29" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="2">
-        <f>D19-D9</f>
-        <v>0.18400000000000005</v>
-      </c>
-      <c r="E29" s="2">
-        <f>E19-E9</f>
-        <v>0.18700000000000006</v>
-      </c>
-      <c r="F29" s="2">
-        <f>F19-F9</f>
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="G29" s="3">
-        <f>G19-G9</f>
-        <v>10.14</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K29" s="2">
-        <f>K19-K9</f>
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="L29" s="2">
-        <f>L19-L9</f>
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="M29" s="3">
-        <f>M19-M9</f>
-        <v>12.5</v>
-      </c>
-      <c r="Q29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="R29" s="7">
-        <f t="shared" si="3"/>
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="S29" s="7">
-        <f t="shared" si="4"/>
-        <v>9.4000000000000083E-2</v>
-      </c>
-      <c r="T29" s="7">
-        <f t="shared" si="4"/>
-        <v>1.9000000000000003E-2</v>
-      </c>
-      <c r="U29" s="8">
-        <f t="shared" si="4"/>
-        <v>-7.5600000000000023</v>
-      </c>
-      <c r="X29" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y29" s="11">
-        <f>AVERAGEA(Y24:Y28)</f>
+      <c r="AD30" s="8">
+        <f>AVERAGEA(AD25:AD29)</f>
         <v>-1.2400000000000033E-2</v>
       </c>
-      <c r="Z29" s="11">
-        <f t="shared" ref="Z29:AA29" si="5">AVERAGEA(Z24:Z28)</f>
+      <c r="AE30" s="8">
+        <f t="shared" ref="AE30:AF30" si="5">AVERAGEA(AE25:AE29)</f>
         <v>9.9999999999997877E-4</v>
       </c>
-      <c r="AA29" s="11">
+      <c r="AF30" s="8">
         <f t="shared" si="5"/>
         <v>-4.0000000000000015E-2</v>
       </c>
-      <c r="AB29" s="12">
-        <f>AVERAGEA(AB24:AB28)</f>
+      <c r="AG30" s="9">
+        <f>AVERAGEA(AG25:AG29)</f>
         <v>-0.83600000000000141</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C30" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="2">
-        <f>D20-D10</f>
-        <v>8.5999999999999965E-2</v>
-      </c>
-      <c r="E30" s="2">
-        <f>E20-E10</f>
-        <v>0.13199999999999995</v>
-      </c>
-      <c r="F30" s="2">
-        <f>F20-F10</f>
-        <v>0.03</v>
-      </c>
-      <c r="G30" s="3">
-        <f>G20-G10</f>
-        <v>10.550000000000004</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="K30" s="2">
-        <f>K20-K10</f>
-        <v>0.03</v>
-      </c>
-      <c r="L30" s="2">
-        <f>L20-L10</f>
-        <v>5.5999999999999994E-2</v>
-      </c>
-      <c r="M30" s="3">
-        <f>M20-M10</f>
-        <v>7.1400000000000006</v>
-      </c>
-      <c r="Q30" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="R30" s="11">
-        <f>AVERAGEA(R25:R29)</f>
-        <v>-3.7800000000000042E-2</v>
-      </c>
-      <c r="S30" s="11">
-        <f t="shared" ref="S30:U30" si="6">AVERAGEA(S25:S29)</f>
-        <v>-1.8800000000000018E-2</v>
-      </c>
-      <c r="T30" s="11">
-        <f t="shared" si="6"/>
-        <v>-7.22E-2</v>
-      </c>
-      <c r="U30" s="12">
-        <f t="shared" si="6"/>
-        <v>-6.7479999999999993</v>
-      </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="C31" s="13" t="s">
+      <c r="AH30" s="23"/>
+      <c r="AI30" s="22"/>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.35">
+      <c r="C31" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="8">
         <f>AVERAGEA(D24:D30)</f>
         <v>0.12300000000000001</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="8">
         <f>AVERAGEA(E24:E30)</f>
         <v>0.12471428571428575</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="8">
         <f>AVERAGEA(F24:F30)</f>
         <v>0.12871428571428573</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="8">
         <f>AVERAGEA(G24:G30)</f>
         <v>8.5414285714285736</v>
       </c>
-      <c r="J31" s="13" t="s">
+      <c r="H31" s="8">
+        <f t="shared" ref="H31:I31" si="6">AVERAGEA(H24:H30)</f>
+        <v>4.1171428571428583</v>
+      </c>
+      <c r="I31" s="9">
+        <f>AVERAGEA(I24:I30)</f>
+        <v>14.541428571428568</v>
+      </c>
+      <c r="L31" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="K31" s="11">
-        <f>AVERAGEA(K24:K30)</f>
+      <c r="M31" s="8">
+        <f>AVERAGEA(M24:M30)</f>
         <v>0.12871428571428573</v>
       </c>
-      <c r="L31" s="11">
-        <f>AVERAGEA(L24:L30)</f>
+      <c r="N31" s="8">
+        <f>AVERAGEA(N24:N30)</f>
         <v>0.19500000000000001</v>
       </c>
-      <c r="M31" s="12">
-        <f>AVERAGEA(M24:M30)</f>
+      <c r="O31" s="9">
+        <f>AVERAGEA(O24:O30)</f>
         <v>8.1614285714285693</v>
       </c>
-      <c r="X31" s="6" t="s">
+      <c r="X31" s="21"/>
+      <c r="Y31" s="21"/>
+      <c r="AH31" s="21"/>
+      <c r="AI31" s="21"/>
+    </row>
+    <row r="33" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC33" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.35">
-      <c r="X32" s="13"/>
-      <c r="Y32" s="13" t="s">
+    <row r="34" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC34" s="10"/>
+      <c r="AD34" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="Z32" s="13" t="s">
+      <c r="AE34" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AA32" s="13" t="s">
+      <c r="AF34" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AB32" s="13" t="s">
+      <c r="AG34" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" spans="24:28" x14ac:dyDescent="0.35">
-      <c r="X33" s="20" t="s">
+      <c r="AH34" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI34" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC35" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="Y33" s="7">
-        <f>Y4-R4</f>
+      <c r="AD35">
+        <f>AD4-T4</f>
         <v>1.3000000000000012E-2</v>
       </c>
-      <c r="Z33" s="7">
-        <f>Z4-S4</f>
+      <c r="AE35">
+        <f>AE4-U4</f>
         <v>4.0000000000000036E-3</v>
       </c>
-      <c r="AA33" s="7">
-        <f>AA4-T4</f>
+      <c r="AF35">
+        <f>AF4-V4</f>
         <v>2.200000000000002E-2</v>
       </c>
-      <c r="AB33" s="8">
-        <f>AB4-U4</f>
+      <c r="AG35" s="24">
+        <f>AG4-W4</f>
         <v>4.4399999999999977</v>
       </c>
-    </row>
-    <row r="34" spans="24:28" x14ac:dyDescent="0.35">
-      <c r="X34" s="20" t="s">
+      <c r="AH35" s="21"/>
+      <c r="AI35" s="2"/>
+    </row>
+    <row r="36" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC36" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="Y34" s="7">
-        <f>Y5-R5</f>
+      <c r="AD36">
+        <f>AD5-T5</f>
         <v>1.5000000000000013E-2</v>
       </c>
-      <c r="Z34" s="7">
-        <f>Z5-S5</f>
+      <c r="AE36">
+        <f>AE5-U5</f>
         <v>4.0000000000000036E-3</v>
       </c>
-      <c r="AA34" s="7">
-        <f>AA5-T5</f>
+      <c r="AF36">
+        <f>AF5-V5</f>
         <v>2.899999999999997E-2</v>
       </c>
-      <c r="AB34" s="8">
-        <f>AB5-U5</f>
+      <c r="AG36" s="25">
+        <f>AG5-W5</f>
         <v>5.1700000000000017</v>
       </c>
-    </row>
-    <row r="35" spans="24:28" x14ac:dyDescent="0.35">
-      <c r="X35" s="20" t="s">
+      <c r="AH36" s="21"/>
+      <c r="AI36" s="2"/>
+    </row>
+    <row r="37" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC37" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="Y35" s="7">
-        <f>Y8-R8</f>
+      <c r="AD37">
+        <f>AD8-T8</f>
         <v>1.2000000000000011E-2</v>
       </c>
-      <c r="Z35" s="7">
-        <f>Z8-S8</f>
+      <c r="AE37">
+        <f>AE8-U8</f>
         <v>8.0000000000000071E-3</v>
       </c>
-      <c r="AA35" s="7">
-        <f>AA8-T8</f>
+      <c r="AF37">
+        <f>AF8-V8</f>
         <v>3.8999999999999979E-2</v>
       </c>
-      <c r="AB35" s="8">
-        <f>AB8-U8</f>
+      <c r="AG37" s="25">
+        <f>AG8-W8</f>
         <v>5.5</v>
       </c>
-    </row>
-    <row r="36" spans="24:28" x14ac:dyDescent="0.35">
-      <c r="X36" s="20" t="s">
+      <c r="AH37" s="21"/>
+      <c r="AI37" s="2"/>
+    </row>
+    <row r="38" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC38" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="Y36" s="7">
-        <f>Y9-R9</f>
+      <c r="AD38">
+        <f>AD9-T9</f>
         <v>2.8000000000000025E-2</v>
       </c>
-      <c r="Z36" s="7">
-        <f>Z9-S9</f>
+      <c r="AE38">
+        <f>AE9-U9</f>
         <v>6.0000000000000053E-3</v>
       </c>
-      <c r="AA36" s="7">
-        <f>AA9-T9</f>
+      <c r="AF38">
+        <f>AF9-V9</f>
         <v>3.4999999999999976E-2</v>
       </c>
-      <c r="AB36" s="8">
-        <f>AB9-U9</f>
+      <c r="AG38" s="25">
+        <f>AG9-W9</f>
         <v>6.2299999999999898</v>
       </c>
-    </row>
-    <row r="37" spans="24:28" x14ac:dyDescent="0.35">
-      <c r="X37" s="20" t="s">
+      <c r="AH38" s="21"/>
+      <c r="AI38" s="2"/>
+    </row>
+    <row r="39" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC39" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="Y37" s="7">
-        <f>Y10-R10</f>
+      <c r="AD39">
+        <f>AD10-T10</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="Z37" s="7">
-        <f>Z10-S10</f>
+      <c r="AE39">
+        <f>AE10-U10</f>
         <v>7.6999999999999957E-2</v>
       </c>
-      <c r="AA37" s="7">
-        <f>AA10-T10</f>
+      <c r="AF39">
+        <f>AF10-V10</f>
         <v>3.6000000000000004E-2</v>
       </c>
-      <c r="AB37" s="8">
-        <f>AB10-U10</f>
+      <c r="AG39" s="25">
+        <f>AG10-W10</f>
         <v>8.2199999999999989</v>
       </c>
-    </row>
-    <row r="38" spans="24:28" x14ac:dyDescent="0.35">
-      <c r="X38" s="13" t="s">
+      <c r="AH39" s="21"/>
+      <c r="AI39" s="2"/>
+    </row>
+    <row r="40" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AC40" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="Y38" s="11">
-        <f>AVERAGEA(Y33:Y37)</f>
+      <c r="AD40" s="8">
+        <f>AVERAGEA(AD35:AD39)</f>
         <v>2.5400000000000013E-2</v>
       </c>
-      <c r="Z38" s="11">
-        <f t="shared" ref="Z38:AB38" si="7">AVERAGEA(Z33:Z37)</f>
+      <c r="AE40" s="8">
+        <f t="shared" ref="AE40:AG40" si="7">AVERAGEA(AE35:AE39)</f>
         <v>1.9799999999999995E-2</v>
       </c>
-      <c r="AA38" s="11">
+      <c r="AF40" s="8">
         <f t="shared" si="7"/>
         <v>3.2199999999999993E-2</v>
       </c>
-      <c r="AB38" s="12">
+      <c r="AG40" s="8">
         <f t="shared" si="7"/>
         <v>5.9119999999999973</v>
       </c>
+      <c r="AH40" s="26"/>
+      <c r="AI40" s="22"/>
+    </row>
+    <row r="41" spans="29:35" x14ac:dyDescent="0.35">
+      <c r="AH41" s="21"/>
+      <c r="AI41" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
